--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-06-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53683CA2-56D4-431C-8FE2-B6CA33E44465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8D1BCE-4420-4214-B41F-856D10C1E6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -334,9 +334,6 @@
     <t>£31.75</t>
   </si>
   <si>
-    <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationuk.co.uk/products/75mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
     <t>£35.53</t>
   </si>
   <si>
@@ -833,6 +830,9 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£36.64</t>
   </si>
 </sst>
 </file>
@@ -1610,131 +1610,131 @@
         <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="H8" t="s">
         <v>93</v>
       </c>
       <c r="I8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" t="s">
         <v>105</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>106</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="s">
         <v>107</v>
       </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>121</v>
+      </c>
+      <c r="O8" t="s">
         <v>108</v>
-      </c>
-      <c r="N8" t="s">
-        <v>122</v>
-      </c>
-      <c r="O8" t="s">
-        <v>109</v>
       </c>
       <c r="P8" t="s">
         <v>30</v>
       </c>
       <c r="Q8" t="s">
+        <v>109</v>
+      </c>
+      <c r="R8" t="s">
         <v>110</v>
-      </c>
-      <c r="R8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
         <v>112</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>113</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" t="s">
         <v>114</v>
       </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>115</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>116</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>117</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>118</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>119</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="s">
         <v>120</v>
       </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" t="s">
-        <v>121</v>
-      </c>
       <c r="N9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P9" t="s">
         <v>30</v>
       </c>
       <c r="Q9" t="s">
+        <v>123</v>
+      </c>
+      <c r="R9" t="s">
         <v>124</v>
-      </c>
-      <c r="R9" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
         <v>126</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>127</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" t="s">
         <v>128</v>
       </c>
-      <c r="D10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>129</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" t="s">
         <v>130</v>
       </c>
-      <c r="H10" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>131</v>
       </c>
-      <c r="J10" t="s">
-        <v>132</v>
-      </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L10" t="s">
         <v>27</v>
@@ -1746,125 +1746,125 @@
         <v>30</v>
       </c>
       <c r="O10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P10" t="s">
         <v>30</v>
       </c>
       <c r="Q10" t="s">
+        <v>134</v>
+      </c>
+      <c r="R10" t="s">
         <v>135</v>
-      </c>
-      <c r="R10" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
         <v>137</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>138</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" t="s">
         <v>139</v>
       </c>
-      <c r="D11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>140</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>141</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>142</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>143</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>144</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
         <v>145</v>
       </c>
-      <c r="L11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
+        <v>157</v>
+      </c>
+      <c r="O11" t="s">
         <v>146</v>
-      </c>
-      <c r="N11" t="s">
-        <v>158</v>
-      </c>
-      <c r="O11" t="s">
-        <v>147</v>
       </c>
       <c r="P11" t="s">
         <v>30</v>
       </c>
       <c r="Q11" t="s">
+        <v>147</v>
+      </c>
+      <c r="R11" t="s">
         <v>148</v>
-      </c>
-      <c r="R11" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
         <v>150</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>151</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
         <v>152</v>
       </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>153</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" t="s">
         <v>154</v>
       </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>155</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
         <v>156</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" t="s">
-        <v>157</v>
       </c>
       <c r="N12" t="s">
         <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s">
         <v>30</v>
       </c>
       <c r="Q12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R12" t="s">
         <v>27</v>
@@ -1872,111 +1872,111 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" t="s">
         <v>161</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>162</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" t="s">
         <v>163</v>
       </c>
-      <c r="D13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E13" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>164</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>165</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>166</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>167</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>168</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
         <v>169</v>
       </c>
-      <c r="L13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
+        <v>195</v>
+      </c>
+      <c r="O13" t="s">
         <v>170</v>
-      </c>
-      <c r="N13" t="s">
-        <v>196</v>
-      </c>
-      <c r="O13" t="s">
-        <v>171</v>
       </c>
       <c r="P13" t="s">
         <v>30</v>
       </c>
       <c r="Q13" t="s">
+        <v>171</v>
+      </c>
+      <c r="R13" t="s">
         <v>172</v>
-      </c>
-      <c r="R13" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" t="s">
         <v>174</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>175</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
         <v>176</v>
       </c>
-      <c r="D14" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>177</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>178</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>179</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>180</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>181</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
         <v>182</v>
       </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>183</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>184</v>
-      </c>
-      <c r="O14" t="s">
-        <v>185</v>
       </c>
       <c r="P14" t="s">
         <v>30</v>
       </c>
       <c r="Q14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R14" t="s">
         <v>27</v>
@@ -1984,55 +1984,55 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" t="s">
         <v>187</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>188</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
         <v>189</v>
       </c>
-      <c r="D15" t="s">
-        <v>189</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" t="s">
         <v>190</v>
       </c>
-      <c r="G15" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>191</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>192</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>193</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
         <v>194</v>
       </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" t="s">
-        <v>195</v>
-      </c>
       <c r="N15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s">
         <v>30</v>
       </c>
       <c r="Q15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R15" t="s">
         <v>27</v>
@@ -2040,69 +2040,69 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" t="s">
         <v>199</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>200</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F16" t="s">
         <v>201</v>
       </c>
-      <c r="D16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>202</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>203</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>204</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>205</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>206</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="s">
         <v>207</v>
       </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" t="s">
-        <v>208</v>
-      </c>
       <c r="N16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P16" t="s">
         <v>30</v>
       </c>
       <c r="Q16" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" t="s">
         <v>211</v>
-      </c>
-      <c r="R16" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" t="s">
         <v>213</v>
       </c>
-      <c r="B17" t="s">
-        <v>214</v>
-      </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
         <v>30</v>
@@ -2152,49 +2152,49 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s">
         <v>215</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>216</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
         <v>217</v>
       </c>
-      <c r="D18" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" t="s">
         <v>218</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" t="s">
-        <v>27</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" t="s">
+        <v>264</v>
+      </c>
+      <c r="O18" t="s">
         <v>219</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" t="s">
-        <v>265</v>
-      </c>
-      <c r="O18" t="s">
-        <v>220</v>
       </c>
       <c r="P18" t="s">
         <v>30</v>
@@ -2203,54 +2203,54 @@
         <v>27</v>
       </c>
       <c r="R18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" t="s">
         <v>222</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>223</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" t="s">
         <v>224</v>
       </c>
-      <c r="D19" t="s">
-        <v>224</v>
-      </c>
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" t="s">
         <v>225</v>
       </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O19" t="s">
         <v>226</v>
-      </c>
-      <c r="K19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" t="s">
-        <v>266</v>
-      </c>
-      <c r="O19" t="s">
-        <v>227</v>
       </c>
       <c r="P19" t="s">
         <v>30</v>
@@ -2259,39 +2259,39 @@
         <v>27</v>
       </c>
       <c r="R19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" t="s">
         <v>229</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>230</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
         <v>231</v>
-      </c>
-      <c r="D20" t="s">
-        <v>231</v>
-      </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" t="s">
-        <v>232</v>
       </c>
       <c r="K20" t="s">
         <v>27</v>
@@ -2320,34 +2320,34 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" t="s">
         <v>233</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>234</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
         <v>235</v>
-      </c>
-      <c r="D21" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" t="s">
-        <v>236</v>
       </c>
       <c r="K21" t="s">
         <v>27</v>
@@ -2376,34 +2376,34 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" t="s">
         <v>237</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>238</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
         <v>239</v>
-      </c>
-      <c r="D22" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" t="s">
-        <v>240</v>
       </c>
       <c r="K22" t="s">
         <v>27</v>
@@ -2432,85 +2432,85 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" t="s">
+        <v>242</v>
+      </c>
+      <c r="F23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="D23" t="s">
-        <v>243</v>
-      </c>
-      <c r="E23" t="s">
-        <v>243</v>
-      </c>
-      <c r="F23" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>244</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" t="s">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
         <v>245</v>
       </c>
-      <c r="I23" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" t="s">
-        <v>269</v>
-      </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
+        <v>266</v>
+      </c>
+      <c r="O23" t="s">
         <v>246</v>
       </c>
-      <c r="N23" t="s">
-        <v>267</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" t="s">
         <v>247</v>
-      </c>
-      <c r="P23" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s">
         <v>249</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" t="s">
+        <v>242</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
         <v>250</v>
       </c>
-      <c r="C24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D24" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>251</v>
       </c>
-      <c r="H24" t="s">
-        <v>252</v>
-      </c>
       <c r="I24" t="s">
         <v>27</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>27</v>
       </c>
       <c r="K24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L24" t="s">
         <v>27</v>
@@ -2527,54 +2527,54 @@
         <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O24" t="s">
+        <v>252</v>
+      </c>
+      <c r="P24" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24" t="s">
         <v>253</v>
-      </c>
-      <c r="P24" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>27</v>
-      </c>
-      <c r="R24" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" t="s">
         <v>255</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>256</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E25" t="s">
+        <v>256</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
         <v>257</v>
       </c>
-      <c r="D25" t="s">
-        <v>257</v>
-      </c>
-      <c r="E25" t="s">
-        <v>257</v>
-      </c>
-      <c r="F25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>258</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" t="s">
         <v>259</v>
-      </c>
-      <c r="I25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" t="s">
-        <v>260</v>
       </c>
       <c r="L25" t="s">
         <v>27</v>
@@ -2583,19 +2583,19 @@
         <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O25" t="s">
+        <v>260</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" t="s">
         <v>261</v>
-      </c>
-      <c r="P25" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-06-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8D1BCE-4420-4214-B41F-856D10C1E6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3555AD53-D495-4320-B705-92824238A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
